--- a/data/trans_orig/P70D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70D_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) en 2023</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>183885</t>
+          <t>184040</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>192653</t>
+          <t>192914</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142085</t>
+          <t>142207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>328726</t>
+          <t>327806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>337060</t>
+          <t>337072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>19118</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11981</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30659</t>
+          <t>29583</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225432</t>
+          <t>227623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>241376</t>
+          <t>242154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151691</t>
+          <t>152559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162974</t>
+          <t>162924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>384151</t>
+          <t>385227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>402829</t>
+          <t>402825</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18947</t>
+          <t>18448</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>13736</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28676</t>
+          <t>30116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133635</t>
+          <t>133500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144350</t>
+          <t>144520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101915</t>
+          <t>102414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113944</t>
+          <t>114055</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>239427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>256035</t>
+          <t>255807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26338</t>
+          <t>25408</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29666</t>
+          <t>28866</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>16450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44299</t>
+          <t>46592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139109</t>
+          <t>140039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157397</t>
+          <t>158096</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>228167</t>
+          <t>228967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>251989</t>
+          <t>252484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378981</t>
+          <t>376688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407230</t>
+          <t>406830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105901</t>
+          <t>105844</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112655</t>
+          <t>112816</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101743</t>
+          <t>101715</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105729</t>
+          <t>105754</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210073</t>
+          <t>210059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217579</t>
+          <t>217675</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17551</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33592</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113763</t>
+          <t>113037</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126971</t>
+          <t>126881</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70548</t>
+          <t>70818</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80337</t>
+          <t>79950</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>187871</t>
+          <t>188322</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>203912</t>
+          <t>204150</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12511</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22566</t>
+          <t>23450</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>320366</t>
+          <t>321949</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>334351</t>
+          <t>333526</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>294904</t>
+          <t>294369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>303683</t>
+          <t>303733</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>620334</t>
+          <t>619450</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>635535</t>
+          <t>635376</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29693</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47074</t>
+          <t>44926</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66437</t>
+          <t>64874</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>597433</t>
+          <t>596425</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>623046</t>
+          <t>622241</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>224937</t>
+          <t>227085</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>253834</t>
+          <t>254463</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>832700</t>
+          <t>834263</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>880427</t>
+          <t>882356</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49777</t>
+          <t>50276</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96815</t>
+          <t>101240</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>67339</t>
+          <t>65658</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>108218</t>
+          <t>105418</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>125685</t>
+          <t>124570</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>196400</t>
+          <t>192169</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1870167</t>
+          <t>1865742</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1917205</t>
+          <t>1916706</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1355425</t>
+          <t>1358225</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1396304</t>
+          <t>1397985</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3234226</t>
+          <t>3238457</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3304941</t>
+          <t>3306056</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70D_R-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>468</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>190164</t>
+          <t>198048</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>184040</t>
+          <t>192636</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>192914</t>
+          <t>200740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>143896</t>
+          <t>152289</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142207</t>
+          <t>150241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>334060</t>
+          <t>350336</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>327806</t>
+          <t>345004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>337072</t>
+          <t>353132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19118</t>
+          <t>19958</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20090</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>13326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29583</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>236049</t>
+          <t>246004</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>227623</t>
+          <t>236610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242154</t>
+          <t>251841</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>158670</t>
+          <t>167036</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>152559</t>
+          <t>160486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162924</t>
+          <t>171651</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>394720</t>
+          <t>413039</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>385227</t>
+          <t>402514</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>402825</t>
+          <t>420194</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15182</t>
+          <t>15109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18448</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30116</t>
+          <t>30513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -1524,17 +1524,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>140153</t>
+          <t>141025</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133500</t>
+          <t>134502</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144520</t>
+          <t>145193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>109226</t>
+          <t>110884</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102414</t>
+          <t>103802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114055</t>
+          <t>115880</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>249378</t>
+          <t>251908</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>239427</t>
+          <t>242127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>255807</t>
+          <t>258665</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25408</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>17613</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28866</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>30478</t>
+          <t>33208</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16450</t>
+          <t>22676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>46859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>150739</t>
+          <t>193854</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140039</t>
+          <t>182856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158096</t>
+          <t>201632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>242063</t>
+          <t>161831</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>228967</t>
+          <t>150563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>252484</t>
+          <t>168933</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>392802</t>
+          <t>355686</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376688</t>
+          <t>342035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>406830</t>
+          <t>366218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>165447</t>
+          <t>209450</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>165447</t>
+          <t>209450</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>165447</t>
+          <t>209450</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>257833</t>
+          <t>179444</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>257833</t>
+          <t>179444</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>257833</t>
+          <t>179444</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>423280</t>
+          <t>388894</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>423280</t>
+          <t>388894</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>423280</t>
+          <t>388894</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>14649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>110356</t>
+          <t>130516</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105844</t>
+          <t>125141</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112816</t>
+          <t>133911</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>104347</t>
+          <t>115545</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101715</t>
+          <t>111718</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105754</t>
+          <t>117379</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>214703</t>
+          <t>246061</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210059</t>
+          <t>240532</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217675</t>
+          <t>250028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>106720</t>
+          <t>119023</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>106720</t>
+          <t>119023</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106720</t>
+          <t>119023</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>220959</t>
+          <t>255181</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>220959</t>
+          <t>255181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>220959</t>
+          <t>255181</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10424</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>15749</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>24646</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17313</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>34149</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>121269</t>
+          <t>121912</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113037</t>
+          <t>114394</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126881</t>
+          <t>127460</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>75978</t>
+          <t>76880</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70818</t>
+          <t>71605</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>79950</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>197247</t>
+          <t>198792</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>188322</t>
+          <t>189289</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>204150</t>
+          <t>205997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>14247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>25711</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>329975</t>
+          <t>383052</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>321949</t>
+          <t>372529</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>333526</t>
+          <t>386851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>300119</t>
+          <t>354764</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>294369</t>
+          <t>348746</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>303733</t>
+          <t>358874</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>630093</t>
+          <t>737816</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>619450</t>
+          <t>726008</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>635376</t>
+          <t>743719</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>335486</t>
+          <t>388726</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>335486</t>
+          <t>388726</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>335486</t>
+          <t>388726</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>307415</t>
+          <t>362993</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>307415</t>
+          <t>362993</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>307415</t>
+          <t>362993</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>642900</t>
+          <t>751719</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>642900</t>
+          <t>751719</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>642900</t>
+          <t>751719</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15751</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30701</t>
+          <t>29283</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>26448</t>
+          <t>27396</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44926</t>
+          <t>38744</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>42199</t>
+          <t>45943</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>34264</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64874</t>
+          <t>59215</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>611375</t>
+          <t>435084</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>596425</t>
+          <t>424349</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>622241</t>
+          <t>442432</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>245563</t>
+          <t>285748</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>227085</t>
+          <t>274400</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>254463</t>
+          <t>292978</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>856938</t>
+          <t>720833</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>834263</t>
+          <t>707561</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>882356</t>
+          <t>732512</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>627126</t>
+          <t>453632</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>627126</t>
+          <t>453632</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>627126</t>
+          <t>453632</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>899137</t>
+          <t>766776</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>899137</t>
+          <t>766776</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>899137</t>
+          <t>766776</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50276</t>
+          <t>67463</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>101240</t>
+          <t>104557</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>65658</t>
+          <t>74678</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>105418</t>
+          <t>108319</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>160684</t>
+          <t>172759</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>124570</t>
+          <t>149857</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>192169</t>
+          <t>202238</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1890078</t>
+          <t>1849495</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1865742</t>
+          <t>1827977</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1916706</t>
+          <t>1865071</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1379863</t>
+          <t>1424976</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1358225</t>
+          <t>1406377</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1397985</t>
+          <t>1440018</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3269942</t>
+          <t>3274471</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3238457</t>
+          <t>3244992</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3306056</t>
+          <t>3297373</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
